--- a/plugins/tensorboard-plugins/tb_plugin/docs/公网URL说明.xlsx
+++ b/plugins/tensorboard-plugins/tb_plugin/docs/公网URL说明.xlsx
@@ -9,7 +9,20 @@
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -36,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="74">
   <si>
     <t>类型</t>
   </si>
@@ -272,18 +285,114 @@
   <si>
     <t>https://repo1.maven.org/maven2/io/swagger/codegen/v3/swagger-codegen-cli/3.0.25/swagger-codegen-cli-3.0.25.jar</t>
   </si>
+  <si>
+    <t>att/plugins/tensorboard-plugins/tb_plugin/setup.py</t>
+  </si>
+  <si>
+    <t>https://gitee.com/ascend/att/tree/master/plugins/tensorboard-plugins/tb_plugin</t>
+  </si>
+  <si>
+    <t>代码仓地址</t>
+  </si>
+  <si>
+    <t>att/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/io/azureblob.py</t>
+  </si>
+  <si>
+    <t>https://trainingdaemon.blob.core.windows.net/tests/test1/test2/test.txt</t>
+  </si>
+  <si>
+    <t>非真实网址，示例远端blob地址</t>
+  </si>
+  <si>
+    <t>att/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/static/trace_script.js</t>
+  </si>
+  <si>
+    <t>http://polymer.github.io/LICENSE.txt</t>
+  </si>
+  <si>
+    <t>polymer框架license</t>
+  </si>
+  <si>
+    <t>http://polymer.github.io/AUTHORS.txt</t>
+  </si>
+  <si>
+    <t>polymer框架作者说明</t>
+  </si>
+  <si>
+    <t>http://polymer.github.io/CONTRIBUTORS.txt</t>
+  </si>
+  <si>
+    <t>polymer框架贡献者说明</t>
+  </si>
+  <si>
+    <t>http://polymer.github.io/PATENTS.txt</t>
+  </si>
+  <si>
+    <t>polymer框架专利说明</t>
+  </si>
+  <si>
+    <t>http://goo.gl/uTcepH</t>
+  </si>
+  <si>
+    <t>非真实网址，示例polyfill，打印内容</t>
+  </si>
+  <si>
+    <t>att/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/static/trace_viewer_full.html</t>
+  </si>
+  <si>
+    <t>https://chromium.googlesource.com/chromium/src/+/master/docs/memory-infra</t>
+  </si>
+  <si>
+    <t>chrome tracing中MemoryInfra性能采集介绍</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com</t>
+  </si>
+  <si>
+    <t>https://developer.android.com</t>
+  </si>
+  <si>
+    <t>https://cs.chromium.org</t>
+  </si>
+  <si>
+    <t>https://cs.chromium.org/search/</t>
+  </si>
+  <si>
+    <t>https://chromium.googlesource.com</t>
+  </si>
+  <si>
+    <t>att/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/static/index.html</t>
+  </si>
+  <si>
+    <t>https://mui.com</t>
+  </si>
+  <si>
+    <t>Mui组件库官网</t>
+  </si>
+  <si>
+    <t>https://reactjs.org/docs/error-decoder.html</t>
+  </si>
+  <si>
+    <t>React官网错误解码网址</t>
+  </si>
+  <si>
+    <t>https://fb.me/react-polyfills</t>
+  </si>
+  <si>
+    <t>React框架polyfill说明</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="28">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -319,6 +428,17 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
@@ -328,13 +448,6 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -790,150 +903,150 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -944,8 +1057,17 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1579,7 +1701,7 @@
       <c r="B19" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="6" t="s">
         <v>34</v>
       </c>
       <c r="D19" t="s">
@@ -1593,7 +1715,7 @@
       <c r="B20" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="7" t="s">
         <v>35</v>
       </c>
       <c r="D20" t="s">
@@ -1607,7 +1729,7 @@
       <c r="B21" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="7" t="s">
         <v>36</v>
       </c>
       <c r="D21" t="s">
@@ -1621,7 +1743,7 @@
       <c r="B22" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="7" t="s">
         <v>38</v>
       </c>
       <c r="D22" t="s">
@@ -1635,7 +1757,7 @@
       <c r="B23" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="7" t="s">
         <v>39</v>
       </c>
       <c r="D23" t="s">
@@ -1649,7 +1771,7 @@
       <c r="B24" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="7" t="s">
         <v>40</v>
       </c>
       <c r="D24" t="s">
@@ -1660,333 +1782,510 @@
       <c r="A25" t="s">
         <v>4</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B25" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="6" t="s">
         <v>41</v>
       </c>
       <c r="D25" t="s">
         <v>17</v>
       </c>
     </row>
+    <row r="26" spans="2:4">
+      <c r="B26" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D26" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4">
+      <c r="B27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4">
+      <c r="B28" t="s">
+        <v>48</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D28" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4">
+      <c r="B29" t="s">
+        <v>48</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4">
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>53</v>
+      </c>
+      <c r="D30" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4">
+      <c r="B31" t="s">
+        <v>48</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4">
+      <c r="B32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="D32" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4">
+      <c r="B33" t="s">
+        <v>59</v>
+      </c>
+      <c r="C33" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D33" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4">
+      <c r="B34" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4">
+      <c r="B35" t="s">
+        <v>59</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4">
+      <c r="B36" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4">
+      <c r="B37" t="s">
+        <v>59</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4">
+      <c r="B38" t="s">
+        <v>59</v>
+      </c>
+      <c r="C38" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4">
+      <c r="B39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C39" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D39" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4">
+      <c r="B40" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4">
+      <c r="B41" t="s">
+        <v>67</v>
+      </c>
+      <c r="C41" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D41" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="42" spans="3:3">
+      <c r="C42" s="10"/>
+    </row>
     <row r="337" ht="14.25" spans="4:4">
-      <c r="D337" s="6"/>
+      <c r="D337" s="11"/>
     </row>
     <row r="338" ht="14.25" spans="4:4">
-      <c r="D338" s="6"/>
+      <c r="D338" s="11"/>
     </row>
     <row r="339" ht="14.25" spans="4:4">
-      <c r="D339" s="6"/>
+      <c r="D339" s="11"/>
     </row>
     <row r="340" spans="3:3">
-      <c r="C340" s="7"/>
+      <c r="C340" s="12"/>
     </row>
     <row r="342" spans="3:3">
-      <c r="C342" s="7"/>
+      <c r="C342" s="12"/>
     </row>
     <row r="343" spans="3:3">
-      <c r="C343" s="7"/>
+      <c r="C343" s="12"/>
     </row>
     <row r="347" spans="3:3">
-      <c r="C347" s="7"/>
+      <c r="C347" s="12"/>
     </row>
     <row r="348" spans="3:3">
-      <c r="C348" s="7"/>
+      <c r="C348" s="12"/>
     </row>
     <row r="349" spans="3:3">
-      <c r="C349" s="7"/>
+      <c r="C349" s="12"/>
     </row>
     <row r="351" spans="3:3">
-      <c r="C351" s="7"/>
+      <c r="C351" s="12"/>
     </row>
     <row r="710" spans="3:3">
-      <c r="C710" s="7"/>
+      <c r="C710" s="12"/>
     </row>
     <row r="711" spans="3:3">
-      <c r="C711" s="7"/>
+      <c r="C711" s="12"/>
     </row>
     <row r="712" spans="3:3">
-      <c r="C712" s="7"/>
+      <c r="C712" s="12"/>
     </row>
     <row r="713" spans="3:3">
-      <c r="C713" s="7"/>
+      <c r="C713" s="12"/>
     </row>
     <row r="714" spans="3:3">
-      <c r="C714" s="7"/>
+      <c r="C714" s="12"/>
     </row>
     <row r="715" spans="3:3">
-      <c r="C715" s="7"/>
+      <c r="C715" s="12"/>
     </row>
     <row r="716" spans="3:3">
-      <c r="C716" s="7"/>
+      <c r="C716" s="12"/>
     </row>
     <row r="717" spans="3:3">
-      <c r="C717" s="7"/>
+      <c r="C717" s="12"/>
     </row>
     <row r="718" spans="3:3">
-      <c r="C718" s="7"/>
+      <c r="C718" s="12"/>
     </row>
     <row r="719" spans="3:3">
-      <c r="C719" s="7"/>
+      <c r="C719" s="12"/>
     </row>
     <row r="720" spans="3:3">
-      <c r="C720" s="7"/>
+      <c r="C720" s="12"/>
     </row>
     <row r="721" spans="3:3">
-      <c r="C721" s="7"/>
+      <c r="C721" s="12"/>
     </row>
     <row r="722" spans="3:3">
-      <c r="C722" s="7"/>
+      <c r="C722" s="12"/>
     </row>
     <row r="723" spans="3:3">
-      <c r="C723" s="7"/>
+      <c r="C723" s="12"/>
     </row>
     <row r="724" spans="3:3">
-      <c r="C724" s="7"/>
+      <c r="C724" s="12"/>
     </row>
     <row r="725" spans="3:3">
-      <c r="C725" s="7"/>
+      <c r="C725" s="12"/>
     </row>
     <row r="726" spans="3:3">
-      <c r="C726" s="7"/>
+      <c r="C726" s="12"/>
     </row>
     <row r="727" spans="3:3">
-      <c r="C727" s="7"/>
+      <c r="C727" s="12"/>
     </row>
     <row r="728" spans="3:3">
-      <c r="C728" s="7"/>
+      <c r="C728" s="12"/>
     </row>
     <row r="729" spans="3:3">
-      <c r="C729" s="7"/>
+      <c r="C729" s="12"/>
     </row>
     <row r="730" spans="3:3">
-      <c r="C730" s="7"/>
+      <c r="C730" s="12"/>
     </row>
     <row r="731" spans="3:3">
-      <c r="C731" s="7"/>
+      <c r="C731" s="12"/>
     </row>
     <row r="732" spans="3:3">
-      <c r="C732" s="7"/>
+      <c r="C732" s="12"/>
     </row>
     <row r="733" spans="3:3">
-      <c r="C733" s="7"/>
+      <c r="C733" s="12"/>
     </row>
     <row r="734" spans="3:3">
-      <c r="C734" s="7"/>
+      <c r="C734" s="12"/>
     </row>
     <row r="735" spans="3:3">
-      <c r="C735" s="7"/>
+      <c r="C735" s="12"/>
     </row>
     <row r="736" spans="3:3">
-      <c r="C736" s="7"/>
+      <c r="C736" s="12"/>
     </row>
     <row r="737" spans="3:3">
-      <c r="C737" s="7"/>
+      <c r="C737" s="12"/>
     </row>
     <row r="738" spans="3:3">
-      <c r="C738" s="7"/>
+      <c r="C738" s="12"/>
     </row>
     <row r="739" spans="3:3">
-      <c r="C739" s="7"/>
+      <c r="C739" s="12"/>
     </row>
     <row r="740" spans="3:3">
-      <c r="C740" s="7"/>
+      <c r="C740" s="12"/>
     </row>
     <row r="741" spans="3:3">
-      <c r="C741" s="7"/>
+      <c r="C741" s="12"/>
     </row>
     <row r="742" spans="3:3">
-      <c r="C742" s="7"/>
+      <c r="C742" s="12"/>
     </row>
     <row r="743" spans="3:3">
-      <c r="C743" s="7"/>
+      <c r="C743" s="12"/>
     </row>
     <row r="744" spans="3:3">
-      <c r="C744" s="7"/>
+      <c r="C744" s="12"/>
     </row>
     <row r="745" spans="3:3">
-      <c r="C745" s="7"/>
+      <c r="C745" s="12"/>
     </row>
     <row r="3157" ht="14.25" spans="2:14">
-      <c r="B3157" s="6"/>
-      <c r="C3157" s="6"/>
-      <c r="D3157" s="6"/>
-      <c r="E3157" s="6"/>
-      <c r="F3157" s="6"/>
-      <c r="G3157" s="6"/>
-      <c r="J3157" s="6"/>
-      <c r="L3157" s="6"/>
-      <c r="M3157" s="6"/>
-      <c r="N3157" s="6"/>
+      <c r="B3157" s="11"/>
+      <c r="C3157" s="11"/>
+      <c r="D3157" s="11"/>
+      <c r="E3157" s="11"/>
+      <c r="F3157" s="11"/>
+      <c r="G3157" s="11"/>
+      <c r="J3157" s="11"/>
+      <c r="L3157" s="11"/>
+      <c r="M3157" s="11"/>
+      <c r="N3157" s="11"/>
     </row>
     <row r="3158" ht="14.25" spans="2:14">
-      <c r="B3158" s="6"/>
-      <c r="C3158" s="6"/>
-      <c r="D3158" s="6"/>
-      <c r="E3158" s="6"/>
-      <c r="F3158" s="6"/>
-      <c r="G3158" s="6"/>
-      <c r="J3158" s="6"/>
-      <c r="L3158" s="6"/>
-      <c r="M3158" s="6"/>
-      <c r="N3158" s="6"/>
+      <c r="B3158" s="11"/>
+      <c r="C3158" s="11"/>
+      <c r="D3158" s="11"/>
+      <c r="E3158" s="11"/>
+      <c r="F3158" s="11"/>
+      <c r="G3158" s="11"/>
+      <c r="J3158" s="11"/>
+      <c r="L3158" s="11"/>
+      <c r="M3158" s="11"/>
+      <c r="N3158" s="11"/>
     </row>
     <row r="3159" ht="14.25" spans="2:14">
-      <c r="B3159" s="6"/>
-      <c r="C3159" s="6"/>
-      <c r="D3159"/>
-      <c r="E3159" s="6"/>
-      <c r="F3159" s="6"/>
-      <c r="G3159" s="6"/>
-      <c r="J3159" s="6"/>
-      <c r="L3159" s="6"/>
-      <c r="M3159" s="6"/>
-      <c r="N3159" s="6"/>
+      <c r="B3159" s="11"/>
+      <c r="C3159" s="11"/>
+      <c r="E3159" s="11"/>
+      <c r="F3159" s="11"/>
+      <c r="G3159" s="11"/>
+      <c r="J3159" s="11"/>
+      <c r="L3159" s="11"/>
+      <c r="M3159" s="11"/>
+      <c r="N3159" s="11"/>
     </row>
     <row r="3160" ht="14.25" spans="2:14">
-      <c r="B3160" s="6"/>
-      <c r="C3160" s="6"/>
-      <c r="D3160"/>
-      <c r="E3160" s="6"/>
-      <c r="F3160" s="6"/>
-      <c r="G3160" s="6"/>
-      <c r="J3160" s="6"/>
-      <c r="L3160" s="6"/>
-      <c r="M3160" s="6"/>
-      <c r="N3160" s="6"/>
+      <c r="B3160" s="11"/>
+      <c r="C3160" s="11"/>
+      <c r="E3160" s="11"/>
+      <c r="F3160" s="11"/>
+      <c r="G3160" s="11"/>
+      <c r="J3160" s="11"/>
+      <c r="L3160" s="11"/>
+      <c r="M3160" s="11"/>
+      <c r="N3160" s="11"/>
     </row>
     <row r="3161" ht="14.25" spans="2:14">
-      <c r="B3161" s="6"/>
-      <c r="C3161" s="6"/>
-      <c r="D3161" s="6"/>
-      <c r="E3161" s="6"/>
-      <c r="F3161" s="6"/>
-      <c r="G3161" s="6"/>
-      <c r="J3161" s="6"/>
-      <c r="L3161" s="6"/>
-      <c r="M3161" s="6"/>
-      <c r="N3161" s="6"/>
+      <c r="B3161" s="11"/>
+      <c r="C3161" s="11"/>
+      <c r="D3161" s="11"/>
+      <c r="E3161" s="11"/>
+      <c r="F3161" s="11"/>
+      <c r="G3161" s="11"/>
+      <c r="J3161" s="11"/>
+      <c r="L3161" s="11"/>
+      <c r="M3161" s="11"/>
+      <c r="N3161" s="11"/>
     </row>
     <row r="3162" ht="14.25" spans="2:14">
-      <c r="B3162" s="6"/>
-      <c r="C3162" s="6"/>
-      <c r="D3162" s="6"/>
-      <c r="E3162" s="6"/>
-      <c r="F3162" s="6"/>
-      <c r="G3162" s="6"/>
-      <c r="J3162" s="6"/>
-      <c r="L3162" s="6"/>
-      <c r="M3162" s="6"/>
-      <c r="N3162" s="6"/>
+      <c r="B3162" s="11"/>
+      <c r="C3162" s="11"/>
+      <c r="D3162" s="11"/>
+      <c r="E3162" s="11"/>
+      <c r="F3162" s="11"/>
+      <c r="G3162" s="11"/>
+      <c r="J3162" s="11"/>
+      <c r="L3162" s="11"/>
+      <c r="M3162" s="11"/>
+      <c r="N3162" s="11"/>
     </row>
     <row r="3163" ht="14.25" spans="2:14">
-      <c r="B3163" s="6"/>
-      <c r="C3163" s="6"/>
-      <c r="D3163" s="6"/>
-      <c r="E3163" s="6"/>
-      <c r="F3163" s="6"/>
-      <c r="G3163" s="6"/>
-      <c r="J3163" s="6"/>
-      <c r="L3163" s="6"/>
-      <c r="M3163" s="6"/>
-      <c r="N3163" s="6"/>
+      <c r="B3163" s="11"/>
+      <c r="C3163" s="11"/>
+      <c r="D3163" s="11"/>
+      <c r="E3163" s="11"/>
+      <c r="F3163" s="11"/>
+      <c r="G3163" s="11"/>
+      <c r="J3163" s="11"/>
+      <c r="L3163" s="11"/>
+      <c r="M3163" s="11"/>
+      <c r="N3163" s="11"/>
     </row>
     <row r="3164" ht="14.25" spans="2:14">
-      <c r="B3164" s="6"/>
-      <c r="C3164" s="6"/>
-      <c r="D3164" s="6"/>
-      <c r="E3164" s="6"/>
-      <c r="F3164" s="6"/>
-      <c r="G3164" s="6"/>
-      <c r="J3164" s="6"/>
-      <c r="L3164" s="6"/>
-      <c r="M3164" s="6"/>
-      <c r="N3164" s="6"/>
+      <c r="B3164" s="11"/>
+      <c r="C3164" s="11"/>
+      <c r="D3164" s="11"/>
+      <c r="E3164" s="11"/>
+      <c r="F3164" s="11"/>
+      <c r="G3164" s="11"/>
+      <c r="J3164" s="11"/>
+      <c r="L3164" s="11"/>
+      <c r="M3164" s="11"/>
+      <c r="N3164" s="11"/>
     </row>
     <row r="3165" ht="14.25" spans="2:14">
-      <c r="B3165" s="6"/>
-      <c r="C3165" s="6"/>
-      <c r="D3165" s="6"/>
-      <c r="E3165" s="6"/>
-      <c r="F3165" s="6"/>
-      <c r="G3165" s="6"/>
-      <c r="J3165" s="6"/>
-      <c r="L3165" s="6"/>
-      <c r="M3165" s="6"/>
-      <c r="N3165" s="6"/>
+      <c r="B3165" s="11"/>
+      <c r="C3165" s="11"/>
+      <c r="D3165" s="11"/>
+      <c r="E3165" s="11"/>
+      <c r="F3165" s="11"/>
+      <c r="G3165" s="11"/>
+      <c r="J3165" s="11"/>
+      <c r="L3165" s="11"/>
+      <c r="M3165" s="11"/>
+      <c r="N3165" s="11"/>
     </row>
     <row r="3166" ht="14.25" spans="2:14">
-      <c r="B3166" s="6"/>
-      <c r="C3166" s="6"/>
-      <c r="D3166" s="6"/>
-      <c r="E3166" s="6"/>
-      <c r="F3166" s="6"/>
-      <c r="G3166" s="6"/>
-      <c r="J3166" s="6"/>
-      <c r="L3166" s="6"/>
-      <c r="M3166" s="6"/>
-      <c r="N3166" s="6"/>
+      <c r="B3166" s="11"/>
+      <c r="C3166" s="11"/>
+      <c r="D3166" s="11"/>
+      <c r="E3166" s="11"/>
+      <c r="F3166" s="11"/>
+      <c r="G3166" s="11"/>
+      <c r="J3166" s="11"/>
+      <c r="L3166" s="11"/>
+      <c r="M3166" s="11"/>
+      <c r="N3166" s="11"/>
     </row>
     <row r="3167" ht="14.25" spans="2:14">
-      <c r="B3167" s="6"/>
-      <c r="C3167" s="6"/>
-      <c r="D3167" s="6"/>
-      <c r="E3167" s="6"/>
-      <c r="F3167" s="6"/>
-      <c r="G3167" s="6"/>
-      <c r="J3167" s="6"/>
-      <c r="L3167" s="6"/>
-      <c r="M3167" s="6"/>
-      <c r="N3167" s="6"/>
+      <c r="B3167" s="11"/>
+      <c r="C3167" s="11"/>
+      <c r="D3167" s="11"/>
+      <c r="E3167" s="11"/>
+      <c r="F3167" s="11"/>
+      <c r="G3167" s="11"/>
+      <c r="J3167" s="11"/>
+      <c r="L3167" s="11"/>
+      <c r="M3167" s="11"/>
+      <c r="N3167" s="11"/>
     </row>
     <row r="3168" ht="14.25" spans="2:14">
-      <c r="B3168" s="6"/>
-      <c r="C3168" s="6"/>
-      <c r="D3168" s="6"/>
-      <c r="E3168" s="6"/>
-      <c r="F3168" s="6"/>
-      <c r="G3168" s="6"/>
-      <c r="J3168" s="6"/>
-      <c r="L3168" s="6"/>
-      <c r="M3168" s="6"/>
-      <c r="N3168" s="6"/>
+      <c r="B3168" s="11"/>
+      <c r="C3168" s="11"/>
+      <c r="D3168" s="11"/>
+      <c r="E3168" s="11"/>
+      <c r="F3168" s="11"/>
+      <c r="G3168" s="11"/>
+      <c r="J3168" s="11"/>
+      <c r="L3168" s="11"/>
+      <c r="M3168" s="11"/>
+      <c r="N3168" s="11"/>
     </row>
     <row r="3169" ht="14.25" spans="2:14">
-      <c r="B3169" s="6"/>
-      <c r="C3169" s="6"/>
-      <c r="D3169" s="6"/>
-      <c r="E3169" s="6"/>
-      <c r="F3169" s="6"/>
-      <c r="G3169" s="6"/>
-      <c r="J3169" s="6"/>
-      <c r="L3169" s="6"/>
-      <c r="M3169" s="6"/>
-      <c r="N3169" s="6"/>
+      <c r="B3169" s="11"/>
+      <c r="C3169" s="11"/>
+      <c r="D3169" s="11"/>
+      <c r="E3169" s="11"/>
+      <c r="F3169" s="11"/>
+      <c r="G3169" s="11"/>
+      <c r="J3169" s="11"/>
+      <c r="L3169" s="11"/>
+      <c r="M3169" s="11"/>
+      <c r="N3169" s="11"/>
     </row>
     <row r="3170" ht="14.25" spans="2:14">
-      <c r="B3170" s="6"/>
-      <c r="C3170" s="6"/>
-      <c r="D3170" s="6"/>
-      <c r="E3170" s="6"/>
-      <c r="F3170" s="6"/>
-      <c r="G3170" s="6"/>
-      <c r="J3170" s="6"/>
-      <c r="L3170" s="6"/>
-      <c r="M3170" s="6"/>
-      <c r="N3170" s="6"/>
+      <c r="B3170" s="11"/>
+      <c r="C3170" s="11"/>
+      <c r="D3170" s="11"/>
+      <c r="E3170" s="11"/>
+      <c r="F3170" s="11"/>
+      <c r="G3170" s="11"/>
+      <c r="J3170" s="11"/>
+      <c r="L3170" s="11"/>
+      <c r="M3170" s="11"/>
+      <c r="N3170" s="11"/>
     </row>
     <row r="3171" ht="14.25" spans="2:14">
-      <c r="B3171" s="6"/>
-      <c r="C3171" s="6"/>
-      <c r="D3171" s="6"/>
-      <c r="E3171" s="6"/>
-      <c r="F3171" s="6"/>
-      <c r="G3171" s="6"/>
-      <c r="J3171" s="6"/>
-      <c r="L3171" s="6"/>
-      <c r="M3171" s="6"/>
-      <c r="N3171" s="6"/>
+      <c r="B3171" s="11"/>
+      <c r="C3171" s="11"/>
+      <c r="D3171" s="11"/>
+      <c r="E3171" s="11"/>
+      <c r="F3171" s="11"/>
+      <c r="G3171" s="11"/>
+      <c r="J3171" s="11"/>
+      <c r="L3171" s="11"/>
+      <c r="M3171" s="11"/>
+      <c r="N3171" s="11"/>
     </row>
   </sheetData>
   <sortState ref="B339:C3155">
@@ -2009,6 +2308,21 @@
     <hyperlink ref="C2" r:id="rId3" display="http://www.apache.org/licenses/LICENSE-2.0" tooltip="http://www.apache.org/licenses/LICENSE-2.0"/>
     <hyperlink ref="C3" r:id="rId4" display="https://pytorch.org/docs/stable/data.html#single-and-multi-process-data-loading"/>
     <hyperlink ref="C12" r:id="rId5" display="https://www.gstatic.com/charts/loader.js"/>
+    <hyperlink ref="C26" r:id="rId6" display="https://gitee.com/ascend/att/tree/master/plugins/tensorboard-plugins/tb_plugin"/>
+    <hyperlink ref="C25" r:id="rId7" display="https://repo1.maven.org/maven2/io/swagger/codegen/v3/swagger-codegen-cli/3.0.25/swagger-codegen-cli-3.0.25.jar" tooltip="https://repo1.maven.org/maven2/io/swagger/codegen/v3/swagger-codegen-cli/3.0.25/swagger-codegen-cli-3.0.25.jar"/>
+    <hyperlink ref="C19" r:id="rId8" display="https://github.com/tensorflow/tensorboard/blob/master/tensorboard/compat/tensorflow_stub/io/gfile.py"/>
+    <hyperlink ref="C29" r:id="rId9" display="http://polymer.github.io/AUTHORS.txt"/>
+    <hyperlink ref="C30" r:id="rId10" display="http://polymer.github.io/CONTRIBUTORS.txt"/>
+    <hyperlink ref="C31" r:id="rId11" display="http://polymer.github.io/PATENTS.txt"/>
+    <hyperlink ref="C32" r:id="rId12" display="http://goo.gl/uTcepH"/>
+    <hyperlink ref="C35" r:id="rId13" display="https://developer.android.com" tooltip="https://developer.android.com"/>
+    <hyperlink ref="C36" r:id="rId14" display="https://cs.chromium.org" tooltip="https://cs.chromium.org"/>
+    <hyperlink ref="C37" r:id="rId15" display="https://cs.chromium.org/search/"/>
+    <hyperlink ref="C38" r:id="rId16" display="https://chromium.googlesource.com" tooltip="https://chromium.googlesource.com"/>
+    <hyperlink ref="C39" r:id="rId17" display="https://mui.com" tooltip="https://mui.com"/>
+    <hyperlink ref="C40" r:id="rId18" display="https://reactjs.org/docs/error-decoder.html"/>
+    <hyperlink ref="C41" r:id="rId19" display="https://fb.me/react-polyfills"/>
+    <hyperlink ref="C27" r:id="rId20" display="https://trainingdaemon.blob.core.windows.net/tests/test1/test2/test.txt"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>

--- a/plugins/tensorboard-plugins/tb_plugin/docs/公网URL说明.xlsx
+++ b/plugins/tensorboard-plugins/tb_plugin/docs/公网URL说明.xlsx
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="84">
   <si>
     <t>类型</t>
   </si>
@@ -175,7 +175,7 @@
     <t>开源软件</t>
   </si>
   <si>
-    <t>att/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/profiler/data.py</t>
+    <t>mstt/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/profiler/data.py</t>
   </si>
   <si>
     <t>http://www.apache.org/licenses/LICENSE-2.0</t>
@@ -220,13 +220,13 @@
     <t>Nvidia官网Apex优化器说明</t>
   </si>
   <si>
-    <t>att/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/profiler/event_parser.py</t>
+    <t>mstt/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/profiler/event_parser.py</t>
   </si>
   <si>
     <t>https://stackoverflow.com/questions/9575409/calling-parent-class-init-with-multiple-inheritance-whats-the-right-way</t>
   </si>
   <si>
-    <t>att/plugins/tensorboard-plugins/tb_plugin/fe/index.html</t>
+    <t>mstt/plugins/tensorboard-plugins/tb_plugin/fe/index.html</t>
   </si>
   <si>
     <t>https://www.gstatic.com/charts/loader.js</t>
@@ -235,7 +235,7 @@
     <t>谷歌图表加载依赖库文件</t>
   </si>
   <si>
-    <t>att/plugins/tensorboard-plugins/tb_plugin/.pre-commit-config.yaml</t>
+    <t>mstt/plugins/tensorboard-plugins/tb_plugin/.pre-commit-config.yaml</t>
   </si>
   <si>
     <t>https://github.com/pre-commit/pre-commit-hooks</t>
@@ -247,7 +247,7 @@
     <t>https://github.com/PyCQA/flake8</t>
   </si>
   <si>
-    <t>att/plugins/tensorboard-plugins/tb_plugin/fe/src/api/generated/api.ts</t>
+    <t>mstt/plugins/tensorboard-plugins/tb_plugin/fe/src/api/generated/api.ts</t>
   </si>
   <si>
     <t>https://github.com/swagger-api/swagger-codegen</t>
@@ -259,7 +259,7 @@
     <t>https://stackoverflow.com/a/7517673/1077943</t>
   </si>
   <si>
-    <t>att/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/io/file.py</t>
+    <t>mstt/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/io/file.py</t>
   </si>
   <si>
     <t>https://github.com/tensorflow/tensorboard/blob/master/tensorboard/compat/tensorflow_stub/io/gfile.py</t>
@@ -271,7 +271,7 @@
     <t>https://docs.min.io/docs/how-to-use-aws-sdk-for-python-with-minio-server.html</t>
   </si>
   <si>
-    <t>att/plugins/tensorboard-plugins/tb_plugin/fe/scripts/setup.sh</t>
+    <t>mstt/plugins/tensorboard-plugins/tb_plugin/fe/scripts/setup.sh</t>
   </si>
   <si>
     <t>https://deb.nodesource.com/setup_16.x</t>
@@ -286,7 +286,7 @@
     <t>https://repo1.maven.org/maven2/io/swagger/codegen/v3/swagger-codegen-cli/3.0.25/swagger-codegen-cli-3.0.25.jar</t>
   </si>
   <si>
-    <t>att/plugins/tensorboard-plugins/tb_plugin/setup.py</t>
+    <t>mstt/plugins/tensorboard-plugins/tb_plugin/setup.py</t>
   </si>
   <si>
     <t>https://gitee.com/ascend/att/tree/master/plugins/tensorboard-plugins/tb_plugin</t>
@@ -295,7 +295,7 @@
     <t>代码仓地址</t>
   </si>
   <si>
-    <t>att/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/io/azureblob.py</t>
+    <t>mstt/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/io/azureblob.py</t>
   </si>
   <si>
     <t>https://trainingdaemon.blob.core.windows.net/tests/test1/test2/test.txt</t>
@@ -304,7 +304,7 @@
     <t>非真实网址，示例远端blob地址</t>
   </si>
   <si>
-    <t>att/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/static/trace_script.js</t>
+    <t>mstt/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/static/trace_script.js</t>
   </si>
   <si>
     <t>http://polymer.github.io/LICENSE.txt</t>
@@ -337,7 +337,7 @@
     <t>非真实网址，示例polyfill，打印内容</t>
   </si>
   <si>
-    <t>att/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/static/trace_viewer_full.html</t>
+    <t>mstt/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/static/trace_viewer_full.html</t>
   </si>
   <si>
     <t>https://chromium.googlesource.com/chromium/src/+/master/docs/memory-infra</t>
@@ -361,7 +361,7 @@
     <t>https://chromium.googlesource.com</t>
   </si>
   <si>
-    <t>att/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/static/index.html</t>
+    <t>mstt/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/static/index.html</t>
   </si>
   <si>
     <t>https://mui.com</t>
@@ -380,6 +380,36 @@
   </si>
   <si>
     <t>React框架polyfill说明</t>
+  </si>
+  <si>
+    <t>mstt/plugins/tensorboard-plugins/tb_plugin/test/test_tensorboard_end2end.py</t>
+  </si>
+  <si>
+    <t>http://{}:{}/data/plugin/pytorch_profiler/</t>
+  </si>
+  <si>
+    <t>测试代码</t>
+  </si>
+  <si>
+    <t>http://{}:{}/{}/data/plugin/pytorch_profiler/</t>
+  </si>
+  <si>
+    <t>https://&lt;account&gt;.blob.core.windows.net</t>
+  </si>
+  <si>
+    <t>mstt/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/utils.py</t>
+  </si>
+  <si>
+    <t>https://github.com/pytorch/pytorch/blob/v1.9.0/torch/csrc/autograd/profiler_kineto.cpp#L33</t>
+  </si>
+  <si>
+    <t>mstt/plugins/tensorboard-plugins/tb_plugin/torch_tb_profiler/profiler/tensor_core.py</t>
+  </si>
+  <si>
+    <t>https://github.com/NVIDIA/PyProf/blob/fd1b2902e3306119eee40ba6b6e8b2f816920c29/pyprof/prof/tc.py#L19</t>
+  </si>
+  <si>
+    <t>https://github.com/pytorch/pytorch/blob/69b2bf70f9c0e591ce5e566afa59e19618031ead/aten/src/ATen/autocast_mode.cpp#L290-L351</t>
   </si>
 </sst>
 </file>
@@ -1046,7 +1076,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1065,7 +1095,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
@@ -1961,331 +1990,394 @@
       <c r="B41" t="s">
         <v>67</v>
       </c>
-      <c r="C41" s="9" t="s">
+      <c r="C41" t="s">
         <v>72</v>
       </c>
       <c r="D41" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="42" spans="3:3">
-      <c r="C42" s="10"/>
+    <row r="42" spans="2:4">
+      <c r="B42" t="s">
+        <v>74</v>
+      </c>
+      <c r="C42" t="s">
+        <v>75</v>
+      </c>
+      <c r="D42" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4">
+      <c r="B43" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" t="s">
+        <v>77</v>
+      </c>
+      <c r="D43" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4">
+      <c r="B44" t="s">
+        <v>33</v>
+      </c>
+      <c r="C44" t="s">
+        <v>78</v>
+      </c>
+      <c r="D44" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4">
+      <c r="B45" t="s">
+        <v>79</v>
+      </c>
+      <c r="C45" t="s">
+        <v>80</v>
+      </c>
+      <c r="D45" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4">
+      <c r="B46" t="s">
+        <v>81</v>
+      </c>
+      <c r="C46" t="s">
+        <v>82</v>
+      </c>
+      <c r="D46" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4">
+      <c r="B47" t="s">
+        <v>81</v>
+      </c>
+      <c r="C47" t="s">
+        <v>83</v>
+      </c>
+      <c r="D47" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="337" ht="14.25" spans="4:4">
-      <c r="D337" s="11"/>
+      <c r="D337" s="10"/>
     </row>
     <row r="338" ht="14.25" spans="4:4">
-      <c r="D338" s="11"/>
+      <c r="D338" s="10"/>
     </row>
     <row r="339" ht="14.25" spans="4:4">
-      <c r="D339" s="11"/>
+      <c r="D339" s="10"/>
     </row>
     <row r="340" spans="3:3">
-      <c r="C340" s="12"/>
+      <c r="C340" s="11"/>
     </row>
     <row r="342" spans="3:3">
-      <c r="C342" s="12"/>
+      <c r="C342" s="11"/>
     </row>
     <row r="343" spans="3:3">
-      <c r="C343" s="12"/>
+      <c r="C343" s="11"/>
     </row>
     <row r="347" spans="3:3">
-      <c r="C347" s="12"/>
+      <c r="C347" s="11"/>
     </row>
     <row r="348" spans="3:3">
-      <c r="C348" s="12"/>
+      <c r="C348" s="11"/>
     </row>
     <row r="349" spans="3:3">
-      <c r="C349" s="12"/>
+      <c r="C349" s="11"/>
     </row>
     <row r="351" spans="3:3">
-      <c r="C351" s="12"/>
+      <c r="C351" s="11"/>
     </row>
     <row r="710" spans="3:3">
-      <c r="C710" s="12"/>
+      <c r="C710" s="11"/>
     </row>
     <row r="711" spans="3:3">
-      <c r="C711" s="12"/>
+      <c r="C711" s="11"/>
     </row>
     <row r="712" spans="3:3">
-      <c r="C712" s="12"/>
+      <c r="C712" s="11"/>
     </row>
     <row r="713" spans="3:3">
-      <c r="C713" s="12"/>
+      <c r="C713" s="11"/>
     </row>
     <row r="714" spans="3:3">
-      <c r="C714" s="12"/>
+      <c r="C714" s="11"/>
     </row>
     <row r="715" spans="3:3">
-      <c r="C715" s="12"/>
+      <c r="C715" s="11"/>
     </row>
     <row r="716" spans="3:3">
-      <c r="C716" s="12"/>
+      <c r="C716" s="11"/>
     </row>
     <row r="717" spans="3:3">
-      <c r="C717" s="12"/>
+      <c r="C717" s="11"/>
     </row>
     <row r="718" spans="3:3">
-      <c r="C718" s="12"/>
+      <c r="C718" s="11"/>
     </row>
     <row r="719" spans="3:3">
-      <c r="C719" s="12"/>
+      <c r="C719" s="11"/>
     </row>
     <row r="720" spans="3:3">
-      <c r="C720" s="12"/>
+      <c r="C720" s="11"/>
     </row>
     <row r="721" spans="3:3">
-      <c r="C721" s="12"/>
+      <c r="C721" s="11"/>
     </row>
     <row r="722" spans="3:3">
-      <c r="C722" s="12"/>
+      <c r="C722" s="11"/>
     </row>
     <row r="723" spans="3:3">
-      <c r="C723" s="12"/>
+      <c r="C723" s="11"/>
     </row>
     <row r="724" spans="3:3">
-      <c r="C724" s="12"/>
+      <c r="C724" s="11"/>
     </row>
     <row r="725" spans="3:3">
-      <c r="C725" s="12"/>
+      <c r="C725" s="11"/>
     </row>
     <row r="726" spans="3:3">
-      <c r="C726" s="12"/>
+      <c r="C726" s="11"/>
     </row>
     <row r="727" spans="3:3">
-      <c r="C727" s="12"/>
+      <c r="C727" s="11"/>
     </row>
     <row r="728" spans="3:3">
-      <c r="C728" s="12"/>
+      <c r="C728" s="11"/>
     </row>
     <row r="729" spans="3:3">
-      <c r="C729" s="12"/>
+      <c r="C729" s="11"/>
     </row>
     <row r="730" spans="3:3">
-      <c r="C730" s="12"/>
+      <c r="C730" s="11"/>
     </row>
     <row r="731" spans="3:3">
-      <c r="C731" s="12"/>
+      <c r="C731" s="11"/>
     </row>
     <row r="732" spans="3:3">
-      <c r="C732" s="12"/>
+      <c r="C732" s="11"/>
     </row>
     <row r="733" spans="3:3">
-      <c r="C733" s="12"/>
+      <c r="C733" s="11"/>
     </row>
     <row r="734" spans="3:3">
-      <c r="C734" s="12"/>
+      <c r="C734" s="11"/>
     </row>
     <row r="735" spans="3:3">
-      <c r="C735" s="12"/>
+      <c r="C735" s="11"/>
     </row>
     <row r="736" spans="3:3">
-      <c r="C736" s="12"/>
+      <c r="C736" s="11"/>
     </row>
     <row r="737" spans="3:3">
-      <c r="C737" s="12"/>
+      <c r="C737" s="11"/>
     </row>
     <row r="738" spans="3:3">
-      <c r="C738" s="12"/>
+      <c r="C738" s="11"/>
     </row>
     <row r="739" spans="3:3">
-      <c r="C739" s="12"/>
+      <c r="C739" s="11"/>
     </row>
     <row r="740" spans="3:3">
-      <c r="C740" s="12"/>
+      <c r="C740" s="11"/>
     </row>
     <row r="741" spans="3:3">
-      <c r="C741" s="12"/>
+      <c r="C741" s="11"/>
     </row>
     <row r="742" spans="3:3">
-      <c r="C742" s="12"/>
+      <c r="C742" s="11"/>
     </row>
     <row r="743" spans="3:3">
-      <c r="C743" s="12"/>
+      <c r="C743" s="11"/>
     </row>
     <row r="744" spans="3:3">
-      <c r="C744" s="12"/>
+      <c r="C744" s="11"/>
     </row>
     <row r="745" spans="3:3">
-      <c r="C745" s="12"/>
+      <c r="C745" s="11"/>
     </row>
     <row r="3157" ht="14.25" spans="2:14">
-      <c r="B3157" s="11"/>
-      <c r="C3157" s="11"/>
-      <c r="D3157" s="11"/>
-      <c r="E3157" s="11"/>
-      <c r="F3157" s="11"/>
-      <c r="G3157" s="11"/>
-      <c r="J3157" s="11"/>
-      <c r="L3157" s="11"/>
-      <c r="M3157" s="11"/>
-      <c r="N3157" s="11"/>
+      <c r="B3157" s="10"/>
+      <c r="C3157" s="10"/>
+      <c r="D3157" s="10"/>
+      <c r="E3157" s="10"/>
+      <c r="F3157" s="10"/>
+      <c r="G3157" s="10"/>
+      <c r="J3157" s="10"/>
+      <c r="L3157" s="10"/>
+      <c r="M3157" s="10"/>
+      <c r="N3157" s="10"/>
     </row>
     <row r="3158" ht="14.25" spans="2:14">
-      <c r="B3158" s="11"/>
-      <c r="C3158" s="11"/>
-      <c r="D3158" s="11"/>
-      <c r="E3158" s="11"/>
-      <c r="F3158" s="11"/>
-      <c r="G3158" s="11"/>
-      <c r="J3158" s="11"/>
-      <c r="L3158" s="11"/>
-      <c r="M3158" s="11"/>
-      <c r="N3158" s="11"/>
+      <c r="B3158" s="10"/>
+      <c r="C3158" s="10"/>
+      <c r="D3158" s="10"/>
+      <c r="E3158" s="10"/>
+      <c r="F3158" s="10"/>
+      <c r="G3158" s="10"/>
+      <c r="J3158" s="10"/>
+      <c r="L3158" s="10"/>
+      <c r="M3158" s="10"/>
+      <c r="N3158" s="10"/>
     </row>
     <row r="3159" ht="14.25" spans="2:14">
-      <c r="B3159" s="11"/>
-      <c r="C3159" s="11"/>
-      <c r="E3159" s="11"/>
-      <c r="F3159" s="11"/>
-      <c r="G3159" s="11"/>
-      <c r="J3159" s="11"/>
-      <c r="L3159" s="11"/>
-      <c r="M3159" s="11"/>
-      <c r="N3159" s="11"/>
+      <c r="B3159" s="10"/>
+      <c r="C3159" s="10"/>
+      <c r="E3159" s="10"/>
+      <c r="F3159" s="10"/>
+      <c r="G3159" s="10"/>
+      <c r="J3159" s="10"/>
+      <c r="L3159" s="10"/>
+      <c r="M3159" s="10"/>
+      <c r="N3159" s="10"/>
     </row>
     <row r="3160" ht="14.25" spans="2:14">
-      <c r="B3160" s="11"/>
-      <c r="C3160" s="11"/>
-      <c r="E3160" s="11"/>
-      <c r="F3160" s="11"/>
-      <c r="G3160" s="11"/>
-      <c r="J3160" s="11"/>
-      <c r="L3160" s="11"/>
-      <c r="M3160" s="11"/>
-      <c r="N3160" s="11"/>
+      <c r="B3160" s="10"/>
+      <c r="C3160" s="10"/>
+      <c r="E3160" s="10"/>
+      <c r="F3160" s="10"/>
+      <c r="G3160" s="10"/>
+      <c r="J3160" s="10"/>
+      <c r="L3160" s="10"/>
+      <c r="M3160" s="10"/>
+      <c r="N3160" s="10"/>
     </row>
     <row r="3161" ht="14.25" spans="2:14">
-      <c r="B3161" s="11"/>
-      <c r="C3161" s="11"/>
-      <c r="D3161" s="11"/>
-      <c r="E3161" s="11"/>
-      <c r="F3161" s="11"/>
-      <c r="G3161" s="11"/>
-      <c r="J3161" s="11"/>
-      <c r="L3161" s="11"/>
-      <c r="M3161" s="11"/>
-      <c r="N3161" s="11"/>
+      <c r="B3161" s="10"/>
+      <c r="C3161" s="10"/>
+      <c r="D3161" s="10"/>
+      <c r="E3161" s="10"/>
+      <c r="F3161" s="10"/>
+      <c r="G3161" s="10"/>
+      <c r="J3161" s="10"/>
+      <c r="L3161" s="10"/>
+      <c r="M3161" s="10"/>
+      <c r="N3161" s="10"/>
     </row>
     <row r="3162" ht="14.25" spans="2:14">
-      <c r="B3162" s="11"/>
-      <c r="C3162" s="11"/>
-      <c r="D3162" s="11"/>
-      <c r="E3162" s="11"/>
-      <c r="F3162" s="11"/>
-      <c r="G3162" s="11"/>
-      <c r="J3162" s="11"/>
-      <c r="L3162" s="11"/>
-      <c r="M3162" s="11"/>
-      <c r="N3162" s="11"/>
+      <c r="B3162" s="10"/>
+      <c r="C3162" s="10"/>
+      <c r="D3162" s="10"/>
+      <c r="E3162" s="10"/>
+      <c r="F3162" s="10"/>
+      <c r="G3162" s="10"/>
+      <c r="J3162" s="10"/>
+      <c r="L3162" s="10"/>
+      <c r="M3162" s="10"/>
+      <c r="N3162" s="10"/>
     </row>
     <row r="3163" ht="14.25" spans="2:14">
-      <c r="B3163" s="11"/>
-      <c r="C3163" s="11"/>
-      <c r="D3163" s="11"/>
-      <c r="E3163" s="11"/>
-      <c r="F3163" s="11"/>
-      <c r="G3163" s="11"/>
-      <c r="J3163" s="11"/>
-      <c r="L3163" s="11"/>
-      <c r="M3163" s="11"/>
-      <c r="N3163" s="11"/>
+      <c r="B3163" s="10"/>
+      <c r="C3163" s="10"/>
+      <c r="D3163" s="10"/>
+      <c r="E3163" s="10"/>
+      <c r="F3163" s="10"/>
+      <c r="G3163" s="10"/>
+      <c r="J3163" s="10"/>
+      <c r="L3163" s="10"/>
+      <c r="M3163" s="10"/>
+      <c r="N3163" s="10"/>
     </row>
     <row r="3164" ht="14.25" spans="2:14">
-      <c r="B3164" s="11"/>
-      <c r="C3164" s="11"/>
-      <c r="D3164" s="11"/>
-      <c r="E3164" s="11"/>
-      <c r="F3164" s="11"/>
-      <c r="G3164" s="11"/>
-      <c r="J3164" s="11"/>
-      <c r="L3164" s="11"/>
-      <c r="M3164" s="11"/>
-      <c r="N3164" s="11"/>
+      <c r="B3164" s="10"/>
+      <c r="C3164" s="10"/>
+      <c r="D3164" s="10"/>
+      <c r="E3164" s="10"/>
+      <c r="F3164" s="10"/>
+      <c r="G3164" s="10"/>
+      <c r="J3164" s="10"/>
+      <c r="L3164" s="10"/>
+      <c r="M3164" s="10"/>
+      <c r="N3164" s="10"/>
     </row>
     <row r="3165" ht="14.25" spans="2:14">
-      <c r="B3165" s="11"/>
-      <c r="C3165" s="11"/>
-      <c r="D3165" s="11"/>
-      <c r="E3165" s="11"/>
-      <c r="F3165" s="11"/>
-      <c r="G3165" s="11"/>
-      <c r="J3165" s="11"/>
-      <c r="L3165" s="11"/>
-      <c r="M3165" s="11"/>
-      <c r="N3165" s="11"/>
+      <c r="B3165" s="10"/>
+      <c r="C3165" s="10"/>
+      <c r="D3165" s="10"/>
+      <c r="E3165" s="10"/>
+      <c r="F3165" s="10"/>
+      <c r="G3165" s="10"/>
+      <c r="J3165" s="10"/>
+      <c r="L3165" s="10"/>
+      <c r="M3165" s="10"/>
+      <c r="N3165" s="10"/>
     </row>
     <row r="3166" ht="14.25" spans="2:14">
-      <c r="B3166" s="11"/>
-      <c r="C3166" s="11"/>
-      <c r="D3166" s="11"/>
-      <c r="E3166" s="11"/>
-      <c r="F3166" s="11"/>
-      <c r="G3166" s="11"/>
-      <c r="J3166" s="11"/>
-      <c r="L3166" s="11"/>
-      <c r="M3166" s="11"/>
-      <c r="N3166" s="11"/>
+      <c r="B3166" s="10"/>
+      <c r="C3166" s="10"/>
+      <c r="D3166" s="10"/>
+      <c r="E3166" s="10"/>
+      <c r="F3166" s="10"/>
+      <c r="G3166" s="10"/>
+      <c r="J3166" s="10"/>
+      <c r="L3166" s="10"/>
+      <c r="M3166" s="10"/>
+      <c r="N3166" s="10"/>
     </row>
     <row r="3167" ht="14.25" spans="2:14">
-      <c r="B3167" s="11"/>
-      <c r="C3167" s="11"/>
-      <c r="D3167" s="11"/>
-      <c r="E3167" s="11"/>
-      <c r="F3167" s="11"/>
-      <c r="G3167" s="11"/>
-      <c r="J3167" s="11"/>
-      <c r="L3167" s="11"/>
-      <c r="M3167" s="11"/>
-      <c r="N3167" s="11"/>
+      <c r="B3167" s="10"/>
+      <c r="C3167" s="10"/>
+      <c r="D3167" s="10"/>
+      <c r="E3167" s="10"/>
+      <c r="F3167" s="10"/>
+      <c r="G3167" s="10"/>
+      <c r="J3167" s="10"/>
+      <c r="L3167" s="10"/>
+      <c r="M3167" s="10"/>
+      <c r="N3167" s="10"/>
     </row>
     <row r="3168" ht="14.25" spans="2:14">
-      <c r="B3168" s="11"/>
-      <c r="C3168" s="11"/>
-      <c r="D3168" s="11"/>
-      <c r="E3168" s="11"/>
-      <c r="F3168" s="11"/>
-      <c r="G3168" s="11"/>
-      <c r="J3168" s="11"/>
-      <c r="L3168" s="11"/>
-      <c r="M3168" s="11"/>
-      <c r="N3168" s="11"/>
+      <c r="B3168" s="10"/>
+      <c r="C3168" s="10"/>
+      <c r="D3168" s="10"/>
+      <c r="E3168" s="10"/>
+      <c r="F3168" s="10"/>
+      <c r="G3168" s="10"/>
+      <c r="J3168" s="10"/>
+      <c r="L3168" s="10"/>
+      <c r="M3168" s="10"/>
+      <c r="N3168" s="10"/>
     </row>
     <row r="3169" ht="14.25" spans="2:14">
-      <c r="B3169" s="11"/>
-      <c r="C3169" s="11"/>
-      <c r="D3169" s="11"/>
-      <c r="E3169" s="11"/>
-      <c r="F3169" s="11"/>
-      <c r="G3169" s="11"/>
-      <c r="J3169" s="11"/>
-      <c r="L3169" s="11"/>
-      <c r="M3169" s="11"/>
-      <c r="N3169" s="11"/>
+      <c r="B3169" s="10"/>
+      <c r="C3169" s="10"/>
+      <c r="D3169" s="10"/>
+      <c r="E3169" s="10"/>
+      <c r="F3169" s="10"/>
+      <c r="G3169" s="10"/>
+      <c r="J3169" s="10"/>
+      <c r="L3169" s="10"/>
+      <c r="M3169" s="10"/>
+      <c r="N3169" s="10"/>
     </row>
     <row r="3170" ht="14.25" spans="2:14">
-      <c r="B3170" s="11"/>
-      <c r="C3170" s="11"/>
-      <c r="D3170" s="11"/>
-      <c r="E3170" s="11"/>
-      <c r="F3170" s="11"/>
-      <c r="G3170" s="11"/>
-      <c r="J3170" s="11"/>
-      <c r="L3170" s="11"/>
-      <c r="M3170" s="11"/>
-      <c r="N3170" s="11"/>
+      <c r="B3170" s="10"/>
+      <c r="C3170" s="10"/>
+      <c r="D3170" s="10"/>
+      <c r="E3170" s="10"/>
+      <c r="F3170" s="10"/>
+      <c r="G3170" s="10"/>
+      <c r="J3170" s="10"/>
+      <c r="L3170" s="10"/>
+      <c r="M3170" s="10"/>
+      <c r="N3170" s="10"/>
     </row>
     <row r="3171" ht="14.25" spans="2:14">
-      <c r="B3171" s="11"/>
-      <c r="C3171" s="11"/>
-      <c r="D3171" s="11"/>
-      <c r="E3171" s="11"/>
-      <c r="F3171" s="11"/>
-      <c r="G3171" s="11"/>
-      <c r="J3171" s="11"/>
-      <c r="L3171" s="11"/>
-      <c r="M3171" s="11"/>
-      <c r="N3171" s="11"/>
+      <c r="B3171" s="10"/>
+      <c r="C3171" s="10"/>
+      <c r="D3171" s="10"/>
+      <c r="E3171" s="10"/>
+      <c r="F3171" s="10"/>
+      <c r="G3171" s="10"/>
+      <c r="J3171" s="10"/>
+      <c r="L3171" s="10"/>
+      <c r="M3171" s="10"/>
+      <c r="N3171" s="10"/>
     </row>
   </sheetData>
   <sortState ref="B339:C3155">
@@ -2308,7 +2400,7 @@
     <hyperlink ref="C2" r:id="rId3" display="http://www.apache.org/licenses/LICENSE-2.0" tooltip="http://www.apache.org/licenses/LICENSE-2.0"/>
     <hyperlink ref="C3" r:id="rId4" display="https://pytorch.org/docs/stable/data.html#single-and-multi-process-data-loading"/>
     <hyperlink ref="C12" r:id="rId5" display="https://www.gstatic.com/charts/loader.js"/>
-    <hyperlink ref="C26" r:id="rId6" display="https://gitee.com/ascend/att/tree/master/plugins/tensorboard-plugins/tb_plugin"/>
+    <hyperlink ref="C26" r:id="rId6" display="https://gitee.com/ascend/att/tree/master/plugins/tensorboard-plugins/tb_plugin" tooltip="https://gitee.com/ascend/att/tree/master/plugins/tensorboard-plugins/tb_plugin"/>
     <hyperlink ref="C25" r:id="rId7" display="https://repo1.maven.org/maven2/io/swagger/codegen/v3/swagger-codegen-cli/3.0.25/swagger-codegen-cli-3.0.25.jar" tooltip="https://repo1.maven.org/maven2/io/swagger/codegen/v3/swagger-codegen-cli/3.0.25/swagger-codegen-cli-3.0.25.jar"/>
     <hyperlink ref="C19" r:id="rId8" display="https://github.com/tensorflow/tensorboard/blob/master/tensorboard/compat/tensorflow_stub/io/gfile.py"/>
     <hyperlink ref="C29" r:id="rId9" display="http://polymer.github.io/AUTHORS.txt"/>

--- a/plugins/tensorboard-plugins/tb_plugin/docs/公网URL说明.xlsx
+++ b/plugins/tensorboard-plugins/tb_plugin/docs/公网URL说明.xlsx
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="86">
   <si>
     <t>类型</t>
   </si>
@@ -411,6 +411,12 @@
   <si>
     <t>https://github.com/pytorch/pytorch/blob/69b2bf70f9c0e591ce5e566afa59e19618031ead/aten/src/ATen/autocast_mode.cpp#L290-L351</t>
   </si>
+  <si>
+    <t>pmail_mindstudio@huawei.com</t>
+  </si>
+  <si>
+    <t>软件作者邮箱</t>
+  </si>
 </sst>
 </file>
 
@@ -469,18 +475,18 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color theme="10"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -948,7 +954,7 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -1095,8 +1101,8 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="6" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2063,321 +2069,332 @@
         <v>17</v>
       </c>
     </row>
+    <row r="48" spans="2:4">
+      <c r="B48" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D48" t="s">
+        <v>85</v>
+      </c>
+    </row>
     <row r="337" ht="14.25" spans="4:4">
-      <c r="D337" s="10"/>
+      <c r="D337" s="11"/>
     </row>
     <row r="338" ht="14.25" spans="4:4">
-      <c r="D338" s="10"/>
+      <c r="D338" s="11"/>
     </row>
     <row r="339" ht="14.25" spans="4:4">
-      <c r="D339" s="10"/>
+      <c r="D339" s="11"/>
     </row>
     <row r="340" spans="3:3">
-      <c r="C340" s="11"/>
+      <c r="C340" s="10"/>
     </row>
     <row r="342" spans="3:3">
-      <c r="C342" s="11"/>
+      <c r="C342" s="10"/>
     </row>
     <row r="343" spans="3:3">
-      <c r="C343" s="11"/>
+      <c r="C343" s="10"/>
     </row>
     <row r="347" spans="3:3">
-      <c r="C347" s="11"/>
+      <c r="C347" s="10"/>
     </row>
     <row r="348" spans="3:3">
-      <c r="C348" s="11"/>
+      <c r="C348" s="10"/>
     </row>
     <row r="349" spans="3:3">
-      <c r="C349" s="11"/>
+      <c r="C349" s="10"/>
     </row>
     <row r="351" spans="3:3">
-      <c r="C351" s="11"/>
+      <c r="C351" s="10"/>
     </row>
     <row r="710" spans="3:3">
-      <c r="C710" s="11"/>
+      <c r="C710" s="10"/>
     </row>
     <row r="711" spans="3:3">
-      <c r="C711" s="11"/>
+      <c r="C711" s="10"/>
     </row>
     <row r="712" spans="3:3">
-      <c r="C712" s="11"/>
+      <c r="C712" s="10"/>
     </row>
     <row r="713" spans="3:3">
-      <c r="C713" s="11"/>
+      <c r="C713" s="10"/>
     </row>
     <row r="714" spans="3:3">
-      <c r="C714" s="11"/>
+      <c r="C714" s="10"/>
     </row>
     <row r="715" spans="3:3">
-      <c r="C715" s="11"/>
+      <c r="C715" s="10"/>
     </row>
     <row r="716" spans="3:3">
-      <c r="C716" s="11"/>
+      <c r="C716" s="10"/>
     </row>
     <row r="717" spans="3:3">
-      <c r="C717" s="11"/>
+      <c r="C717" s="10"/>
     </row>
     <row r="718" spans="3:3">
-      <c r="C718" s="11"/>
+      <c r="C718" s="10"/>
     </row>
     <row r="719" spans="3:3">
-      <c r="C719" s="11"/>
+      <c r="C719" s="10"/>
     </row>
     <row r="720" spans="3:3">
-      <c r="C720" s="11"/>
+      <c r="C720" s="10"/>
     </row>
     <row r="721" spans="3:3">
-      <c r="C721" s="11"/>
+      <c r="C721" s="10"/>
     </row>
     <row r="722" spans="3:3">
-      <c r="C722" s="11"/>
+      <c r="C722" s="10"/>
     </row>
     <row r="723" spans="3:3">
-      <c r="C723" s="11"/>
+      <c r="C723" s="10"/>
     </row>
     <row r="724" spans="3:3">
-      <c r="C724" s="11"/>
+      <c r="C724" s="10"/>
     </row>
     <row r="725" spans="3:3">
-      <c r="C725" s="11"/>
+      <c r="C725" s="10"/>
     </row>
     <row r="726" spans="3:3">
-      <c r="C726" s="11"/>
+      <c r="C726" s="10"/>
     </row>
     <row r="727" spans="3:3">
-      <c r="C727" s="11"/>
+      <c r="C727" s="10"/>
     </row>
     <row r="728" spans="3:3">
-      <c r="C728" s="11"/>
+      <c r="C728" s="10"/>
     </row>
     <row r="729" spans="3:3">
-      <c r="C729" s="11"/>
+      <c r="C729" s="10"/>
     </row>
     <row r="730" spans="3:3">
-      <c r="C730" s="11"/>
+      <c r="C730" s="10"/>
     </row>
     <row r="731" spans="3:3">
-      <c r="C731" s="11"/>
+      <c r="C731" s="10"/>
     </row>
     <row r="732" spans="3:3">
-      <c r="C732" s="11"/>
+      <c r="C732" s="10"/>
     </row>
     <row r="733" spans="3:3">
-      <c r="C733" s="11"/>
+      <c r="C733" s="10"/>
     </row>
     <row r="734" spans="3:3">
-      <c r="C734" s="11"/>
+      <c r="C734" s="10"/>
     </row>
     <row r="735" spans="3:3">
-      <c r="C735" s="11"/>
+      <c r="C735" s="10"/>
     </row>
     <row r="736" spans="3:3">
-      <c r="C736" s="11"/>
+      <c r="C736" s="10"/>
     </row>
     <row r="737" spans="3:3">
-      <c r="C737" s="11"/>
+      <c r="C737" s="10"/>
     </row>
     <row r="738" spans="3:3">
-      <c r="C738" s="11"/>
+      <c r="C738" s="10"/>
     </row>
     <row r="739" spans="3:3">
-      <c r="C739" s="11"/>
+      <c r="C739" s="10"/>
     </row>
     <row r="740" spans="3:3">
-      <c r="C740" s="11"/>
+      <c r="C740" s="10"/>
     </row>
     <row r="741" spans="3:3">
-      <c r="C741" s="11"/>
+      <c r="C741" s="10"/>
     </row>
     <row r="742" spans="3:3">
-      <c r="C742" s="11"/>
+      <c r="C742" s="10"/>
     </row>
     <row r="743" spans="3:3">
-      <c r="C743" s="11"/>
+      <c r="C743" s="10"/>
     </row>
     <row r="744" spans="3:3">
-      <c r="C744" s="11"/>
+      <c r="C744" s="10"/>
     </row>
     <row r="745" spans="3:3">
-      <c r="C745" s="11"/>
+      <c r="C745" s="10"/>
     </row>
     <row r="3157" ht="14.25" spans="2:14">
-      <c r="B3157" s="10"/>
-      <c r="C3157" s="10"/>
-      <c r="D3157" s="10"/>
-      <c r="E3157" s="10"/>
-      <c r="F3157" s="10"/>
-      <c r="G3157" s="10"/>
-      <c r="J3157" s="10"/>
-      <c r="L3157" s="10"/>
-      <c r="M3157" s="10"/>
-      <c r="N3157" s="10"/>
+      <c r="B3157" s="11"/>
+      <c r="C3157" s="11"/>
+      <c r="D3157" s="11"/>
+      <c r="E3157" s="11"/>
+      <c r="F3157" s="11"/>
+      <c r="G3157" s="11"/>
+      <c r="J3157" s="11"/>
+      <c r="L3157" s="11"/>
+      <c r="M3157" s="11"/>
+      <c r="N3157" s="11"/>
     </row>
     <row r="3158" ht="14.25" spans="2:14">
-      <c r="B3158" s="10"/>
-      <c r="C3158" s="10"/>
-      <c r="D3158" s="10"/>
-      <c r="E3158" s="10"/>
-      <c r="F3158" s="10"/>
-      <c r="G3158" s="10"/>
-      <c r="J3158" s="10"/>
-      <c r="L3158" s="10"/>
-      <c r="M3158" s="10"/>
-      <c r="N3158" s="10"/>
+      <c r="B3158" s="11"/>
+      <c r="C3158" s="11"/>
+      <c r="D3158" s="11"/>
+      <c r="E3158" s="11"/>
+      <c r="F3158" s="11"/>
+      <c r="G3158" s="11"/>
+      <c r="J3158" s="11"/>
+      <c r="L3158" s="11"/>
+      <c r="M3158" s="11"/>
+      <c r="N3158" s="11"/>
     </row>
     <row r="3159" ht="14.25" spans="2:14">
-      <c r="B3159" s="10"/>
-      <c r="C3159" s="10"/>
-      <c r="E3159" s="10"/>
-      <c r="F3159" s="10"/>
-      <c r="G3159" s="10"/>
-      <c r="J3159" s="10"/>
-      <c r="L3159" s="10"/>
-      <c r="M3159" s="10"/>
-      <c r="N3159" s="10"/>
+      <c r="B3159" s="11"/>
+      <c r="C3159" s="11"/>
+      <c r="E3159" s="11"/>
+      <c r="F3159" s="11"/>
+      <c r="G3159" s="11"/>
+      <c r="J3159" s="11"/>
+      <c r="L3159" s="11"/>
+      <c r="M3159" s="11"/>
+      <c r="N3159" s="11"/>
     </row>
     <row r="3160" ht="14.25" spans="2:14">
-      <c r="B3160" s="10"/>
-      <c r="C3160" s="10"/>
-      <c r="E3160" s="10"/>
-      <c r="F3160" s="10"/>
-      <c r="G3160" s="10"/>
-      <c r="J3160" s="10"/>
-      <c r="L3160" s="10"/>
-      <c r="M3160" s="10"/>
-      <c r="N3160" s="10"/>
+      <c r="B3160" s="11"/>
+      <c r="C3160" s="11"/>
+      <c r="E3160" s="11"/>
+      <c r="F3160" s="11"/>
+      <c r="G3160" s="11"/>
+      <c r="J3160" s="11"/>
+      <c r="L3160" s="11"/>
+      <c r="M3160" s="11"/>
+      <c r="N3160" s="11"/>
     </row>
     <row r="3161" ht="14.25" spans="2:14">
-      <c r="B3161" s="10"/>
-      <c r="C3161" s="10"/>
-      <c r="D3161" s="10"/>
-      <c r="E3161" s="10"/>
-      <c r="F3161" s="10"/>
-      <c r="G3161" s="10"/>
-      <c r="J3161" s="10"/>
-      <c r="L3161" s="10"/>
-      <c r="M3161" s="10"/>
-      <c r="N3161" s="10"/>
+      <c r="B3161" s="11"/>
+      <c r="C3161" s="11"/>
+      <c r="D3161" s="11"/>
+      <c r="E3161" s="11"/>
+      <c r="F3161" s="11"/>
+      <c r="G3161" s="11"/>
+      <c r="J3161" s="11"/>
+      <c r="L3161" s="11"/>
+      <c r="M3161" s="11"/>
+      <c r="N3161" s="11"/>
     </row>
     <row r="3162" ht="14.25" spans="2:14">
-      <c r="B3162" s="10"/>
-      <c r="C3162" s="10"/>
-      <c r="D3162" s="10"/>
-      <c r="E3162" s="10"/>
-      <c r="F3162" s="10"/>
-      <c r="G3162" s="10"/>
-      <c r="J3162" s="10"/>
-      <c r="L3162" s="10"/>
-      <c r="M3162" s="10"/>
-      <c r="N3162" s="10"/>
+      <c r="B3162" s="11"/>
+      <c r="C3162" s="11"/>
+      <c r="D3162" s="11"/>
+      <c r="E3162" s="11"/>
+      <c r="F3162" s="11"/>
+      <c r="G3162" s="11"/>
+      <c r="J3162" s="11"/>
+      <c r="L3162" s="11"/>
+      <c r="M3162" s="11"/>
+      <c r="N3162" s="11"/>
     </row>
     <row r="3163" ht="14.25" spans="2:14">
-      <c r="B3163" s="10"/>
-      <c r="C3163" s="10"/>
-      <c r="D3163" s="10"/>
-      <c r="E3163" s="10"/>
-      <c r="F3163" s="10"/>
-      <c r="G3163" s="10"/>
-      <c r="J3163" s="10"/>
-      <c r="L3163" s="10"/>
-      <c r="M3163" s="10"/>
-      <c r="N3163" s="10"/>
+      <c r="B3163" s="11"/>
+      <c r="C3163" s="11"/>
+      <c r="D3163" s="11"/>
+      <c r="E3163" s="11"/>
+      <c r="F3163" s="11"/>
+      <c r="G3163" s="11"/>
+      <c r="J3163" s="11"/>
+      <c r="L3163" s="11"/>
+      <c r="M3163" s="11"/>
+      <c r="N3163" s="11"/>
     </row>
     <row r="3164" ht="14.25" spans="2:14">
-      <c r="B3164" s="10"/>
-      <c r="C3164" s="10"/>
-      <c r="D3164" s="10"/>
-      <c r="E3164" s="10"/>
-      <c r="F3164" s="10"/>
-      <c r="G3164" s="10"/>
-      <c r="J3164" s="10"/>
-      <c r="L3164" s="10"/>
-      <c r="M3164" s="10"/>
-      <c r="N3164" s="10"/>
+      <c r="B3164" s="11"/>
+      <c r="C3164" s="11"/>
+      <c r="D3164" s="11"/>
+      <c r="E3164" s="11"/>
+      <c r="F3164" s="11"/>
+      <c r="G3164" s="11"/>
+      <c r="J3164" s="11"/>
+      <c r="L3164" s="11"/>
+      <c r="M3164" s="11"/>
+      <c r="N3164" s="11"/>
     </row>
     <row r="3165" ht="14.25" spans="2:14">
-      <c r="B3165" s="10"/>
-      <c r="C3165" s="10"/>
-      <c r="D3165" s="10"/>
-      <c r="E3165" s="10"/>
-      <c r="F3165" s="10"/>
-      <c r="G3165" s="10"/>
-      <c r="J3165" s="10"/>
-      <c r="L3165" s="10"/>
-      <c r="M3165" s="10"/>
-      <c r="N3165" s="10"/>
+      <c r="B3165" s="11"/>
+      <c r="C3165" s="11"/>
+      <c r="D3165" s="11"/>
+      <c r="E3165" s="11"/>
+      <c r="F3165" s="11"/>
+      <c r="G3165" s="11"/>
+      <c r="J3165" s="11"/>
+      <c r="L3165" s="11"/>
+      <c r="M3165" s="11"/>
+      <c r="N3165" s="11"/>
     </row>
     <row r="3166" ht="14.25" spans="2:14">
-      <c r="B3166" s="10"/>
-      <c r="C3166" s="10"/>
-      <c r="D3166" s="10"/>
-      <c r="E3166" s="10"/>
-      <c r="F3166" s="10"/>
-      <c r="G3166" s="10"/>
-      <c r="J3166" s="10"/>
-      <c r="L3166" s="10"/>
-      <c r="M3166" s="10"/>
-      <c r="N3166" s="10"/>
+      <c r="B3166" s="11"/>
+      <c r="C3166" s="11"/>
+      <c r="D3166" s="11"/>
+      <c r="E3166" s="11"/>
+      <c r="F3166" s="11"/>
+      <c r="G3166" s="11"/>
+      <c r="J3166" s="11"/>
+      <c r="L3166" s="11"/>
+      <c r="M3166" s="11"/>
+      <c r="N3166" s="11"/>
     </row>
     <row r="3167" ht="14.25" spans="2:14">
-      <c r="B3167" s="10"/>
-      <c r="C3167" s="10"/>
-      <c r="D3167" s="10"/>
-      <c r="E3167" s="10"/>
-      <c r="F3167" s="10"/>
-      <c r="G3167" s="10"/>
-      <c r="J3167" s="10"/>
-      <c r="L3167" s="10"/>
-      <c r="M3167" s="10"/>
-      <c r="N3167" s="10"/>
+      <c r="B3167" s="11"/>
+      <c r="C3167" s="11"/>
+      <c r="D3167" s="11"/>
+      <c r="E3167" s="11"/>
+      <c r="F3167" s="11"/>
+      <c r="G3167" s="11"/>
+      <c r="J3167" s="11"/>
+      <c r="L3167" s="11"/>
+      <c r="M3167" s="11"/>
+      <c r="N3167" s="11"/>
     </row>
     <row r="3168" ht="14.25" spans="2:14">
-      <c r="B3168" s="10"/>
-      <c r="C3168" s="10"/>
-      <c r="D3168" s="10"/>
-      <c r="E3168" s="10"/>
-      <c r="F3168" s="10"/>
-      <c r="G3168" s="10"/>
-      <c r="J3168" s="10"/>
-      <c r="L3168" s="10"/>
-      <c r="M3168" s="10"/>
-      <c r="N3168" s="10"/>
+      <c r="B3168" s="11"/>
+      <c r="C3168" s="11"/>
+      <c r="D3168" s="11"/>
+      <c r="E3168" s="11"/>
+      <c r="F3168" s="11"/>
+      <c r="G3168" s="11"/>
+      <c r="J3168" s="11"/>
+      <c r="L3168" s="11"/>
+      <c r="M3168" s="11"/>
+      <c r="N3168" s="11"/>
     </row>
     <row r="3169" ht="14.25" spans="2:14">
-      <c r="B3169" s="10"/>
-      <c r="C3169" s="10"/>
-      <c r="D3169" s="10"/>
-      <c r="E3169" s="10"/>
-      <c r="F3169" s="10"/>
-      <c r="G3169" s="10"/>
-      <c r="J3169" s="10"/>
-      <c r="L3169" s="10"/>
-      <c r="M3169" s="10"/>
-      <c r="N3169" s="10"/>
+      <c r="B3169" s="11"/>
+      <c r="C3169" s="11"/>
+      <c r="D3169" s="11"/>
+      <c r="E3169" s="11"/>
+      <c r="F3169" s="11"/>
+      <c r="G3169" s="11"/>
+      <c r="J3169" s="11"/>
+      <c r="L3169" s="11"/>
+      <c r="M3169" s="11"/>
+      <c r="N3169" s="11"/>
     </row>
     <row r="3170" ht="14.25" spans="2:14">
-      <c r="B3170" s="10"/>
-      <c r="C3170" s="10"/>
-      <c r="D3170" s="10"/>
-      <c r="E3170" s="10"/>
-      <c r="F3170" s="10"/>
-      <c r="G3170" s="10"/>
-      <c r="J3170" s="10"/>
-      <c r="L3170" s="10"/>
-      <c r="M3170" s="10"/>
-      <c r="N3170" s="10"/>
+      <c r="B3170" s="11"/>
+      <c r="C3170" s="11"/>
+      <c r="D3170" s="11"/>
+      <c r="E3170" s="11"/>
+      <c r="F3170" s="11"/>
+      <c r="G3170" s="11"/>
+      <c r="J3170" s="11"/>
+      <c r="L3170" s="11"/>
+      <c r="M3170" s="11"/>
+      <c r="N3170" s="11"/>
     </row>
     <row r="3171" ht="14.25" spans="2:14">
-      <c r="B3171" s="10"/>
-      <c r="C3171" s="10"/>
-      <c r="D3171" s="10"/>
-      <c r="E3171" s="10"/>
-      <c r="F3171" s="10"/>
-      <c r="G3171" s="10"/>
-      <c r="J3171" s="10"/>
-      <c r="L3171" s="10"/>
-      <c r="M3171" s="10"/>
-      <c r="N3171" s="10"/>
+      <c r="B3171" s="11"/>
+      <c r="C3171" s="11"/>
+      <c r="D3171" s="11"/>
+      <c r="E3171" s="11"/>
+      <c r="F3171" s="11"/>
+      <c r="G3171" s="11"/>
+      <c r="J3171" s="11"/>
+      <c r="L3171" s="11"/>
+      <c r="M3171" s="11"/>
+      <c r="N3171" s="11"/>
     </row>
   </sheetData>
   <sortState ref="B339:C3155">
@@ -2415,6 +2432,7 @@
     <hyperlink ref="C40" r:id="rId18" display="https://reactjs.org/docs/error-decoder.html"/>
     <hyperlink ref="C41" r:id="rId19" display="https://fb.me/react-polyfills"/>
     <hyperlink ref="C27" r:id="rId20" display="https://trainingdaemon.blob.core.windows.net/tests/test1/test2/test.txt"/>
+    <hyperlink ref="C48" r:id="rId21" display="pmail_mindstudio@huawei.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="180" verticalDpi="180"/>
